--- a/Config/Excel/BattlePlayer@玩家配置/BattlePlayerConfig@cs.xlsx
+++ b/Config/Excel/BattlePlayer@玩家配置/BattlePlayerConfig@cs.xlsx
@@ -27,33 +27,39 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+  <si>
+    <t>#</t>
+  </si>
   <si>
     <t>Id</t>
   </si>
   <si>
+    <t>Note说明</t>
+  </si>
+  <si>
+    <t>资源</t>
+  </si>
+  <si>
     <t>普攻技能</t>
   </si>
   <si>
-    <t>资源</t>
-  </si>
-  <si>
-    <t>#Note</t>
-  </si>
-  <si>
-    <t>SkillIds</t>
+    <t>Note</t>
   </si>
   <si>
     <t>Asset</t>
   </si>
   <si>
+    <t>AttackSkill</t>
+  </si>
+  <si>
     <t>long</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
-    <t>long[]</t>
+    <t>int</t>
   </si>
   <si>
     <t>普通测试玩家</t>
@@ -72,13 +78,34 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -225,7 +252,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -234,121 +261,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -545,145 +578,153 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -996,86 +1037,112 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A2:F15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="4" max="4" width="20.125" customWidth="1"/>
-    <col min="5" max="5" width="28.375" customWidth="1"/>
-    <col min="6" max="6" width="19.5" customWidth="1"/>
-    <col min="7" max="7" width="19.875" customWidth="1"/>
+    <col min="5" max="5" width="19.5" customWidth="1"/>
+    <col min="6" max="6" width="22.25" style="2" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="2" spans="1:6">
+      <c r="D2" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
     <row r="3" s="1" customFormat="1" spans="1:6">
-      <c r="C3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="D3" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="E3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:6">
-      <c r="C4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="C4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="E4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:6">
-      <c r="C5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2">
+      <c r="D5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" ht="13.5" spans="1:6">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5">
         <v>1</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6">
+      <c r="D6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6">
         <v>101</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="6"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="6"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="F9" s="2"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="F15" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
